--- a/data/voitures.xlsx
+++ b/data/voitures.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10332"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Voitures" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Valeurs autorisees" state="visible" r:id="rId5"/>
+    <sheet name="Voitures" sheetId="1" r:id="rId1"/>
+    <sheet name="Valeurs autorisees" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -47,9 +50,6 @@
     <t>Renault</t>
   </si>
   <si>
-    <t>Clio 5</t>
-  </si>
-  <si>
     <t>Citadine</t>
   </si>
   <si>
@@ -59,9 +59,6 @@
     <t>Essence</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1541899481282-d53bffe3c35d?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
-  </si>
-  <si>
     <t>Oui</t>
   </si>
   <si>
@@ -165,26 +162,44 @@
   </si>
   <si>
     <t>Électrique</t>
+  </si>
+  <si>
+    <t>Captur</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1623826631942-5d55cf980120?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -209,15 +224,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -234,7 +252,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -244,44 +262,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -311,12 +329,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -355,208 +373,149 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="5" width="14" customWidth="1"/>
@@ -567,7 +526,7 @@
     <col min="10" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -599,246 +558,249 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2">
+        <v>5000</v>
+      </c>
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="D2">
-        <v>4000</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
       </c>
       <c r="G2">
         <v>5</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
       </c>
       <c r="D3">
         <v>6500</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
       <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
         <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
       </c>
       <c r="D4">
         <v>7000</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
       <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="I4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>4200</v>
       </c>
       <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
         <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
       </c>
       <c r="G5">
         <v>5</v>
       </c>
       <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" t="s">
         <v>32</v>
       </c>
-      <c r="I5" t="s">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>33</v>
       </c>
-      <c r="J5" t="s">
+      <c r="B6" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>8000</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>37</v>
       </c>
-      <c r="I6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="B7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C7" t="s">
         <v>39</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>41</v>
       </c>
       <c r="D7">
         <v>15000</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8">
         <v>5000</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -852,78 +814,78 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
         <v>48</v>
       </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
       <c r="D5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/data/voitures.xlsx
+++ b/data/voitures.xlsx
@@ -167,7 +167,7 @@
     <t>Captur</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1623826631942-5d55cf980120?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+    <t>https://images.unsplash.com/photo-1563455762146-d91d5ac83925?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
   </si>
 </sst>
 </file>
